--- a/shapefile/kbliUpdated.xlsx
+++ b/shapefile/kbliUpdated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BPS\1. Orientasi Kerja\03. Dashboard SE BPS Sijunjung\shapefile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A2E32FD-AC24-47E5-AA74-D75A137CAD63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4A4FB2-CEA5-4684-8045-D6F4C10CE1DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="624">
   <si>
     <t>01270</t>
   </si>
@@ -1897,6 +1897,15 @@
   </si>
   <si>
     <t>Keterangan</t>
+  </si>
+  <si>
+    <t>Jasa Pekerjaan Konstruksi Prapabrikasi Bangunan Gedung</t>
+  </si>
+  <si>
+    <t>Perdagangan Besar Suku Cadang Sepeda Motor Dan Aksesorinya</t>
+  </si>
+  <si>
+    <t>Perdagangan Eceran Barang Kerajinan Dan Lukisan Lainnya</t>
   </si>
 </sst>
 </file>
@@ -2322,6 +2331,9 @@
       <c r="A5" t="s">
         <v>3</v>
       </c>
+      <c r="B5" t="s">
+        <v>621</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
@@ -2727,6 +2739,9 @@
       <c r="A56" s="4" t="s">
         <v>54</v>
       </c>
+      <c r="B56" t="s">
+        <v>621</v>
+      </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
@@ -2849,6 +2864,9 @@
       <c r="A72" t="s">
         <v>70</v>
       </c>
+      <c r="B72" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
@@ -3133,6 +3151,9 @@
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>106</v>
+      </c>
+      <c r="B108" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
